--- a/Result/profitability/6438.xlsx
+++ b/Result/profitability/6438.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM53"/>
+  <dimension ref="A1:AM54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7161,6 +7161,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>6438</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1824</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1352</v>
+      </c>
+      <c r="E54" t="n">
+        <v>472</v>
+      </c>
+      <c r="F54" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="G54" t="n">
+        <v>207</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>11.35%</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>211</v>
+      </c>
+      <c r="K54" t="n">
+        <v>166</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.69875</v>
+      </c>
+      <c r="N54" t="n">
+        <v>24.275</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0.1477272727272727</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-0.5399999999999991</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-0.0204468004543733</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.1744186046511629</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>-1.419999999999998</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>-0.05203371198241102</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
